--- a/artfynd/A 8803-2026 artfynd.xlsx
+++ b/artfynd/A 8803-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113381963</v>
+        <v>113381831</v>
       </c>
       <c r="B2" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477635</v>
+        <v>477779</v>
       </c>
       <c r="R2" t="n">
-        <v>6582136</v>
+        <v>6582487</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113381809</v>
+        <v>113381769</v>
       </c>
       <c r="B3" t="n">
-        <v>94071</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2813</v>
+        <v>2668</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477606</v>
+        <v>477706</v>
       </c>
       <c r="R3" t="n">
-        <v>6582142</v>
+        <v>6582294</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113381831</v>
+        <v>113381770</v>
       </c>
       <c r="B4" t="n">
-        <v>94158</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477779</v>
+        <v>477702</v>
       </c>
       <c r="R4" t="n">
-        <v>6582487</v>
+        <v>6582342</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -973,11 +963,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,12 +986,7 @@
         <v>113381772</v>
       </c>
       <c r="B5" t="n">
-        <v>94162</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,6 +1077,410 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113381827</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skråmforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477712</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6582313</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113381809</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skråmforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477606</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6582142</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113381963</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skråmforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477635</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6582136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113381964</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skråmforsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477705</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6582292</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 8803-2026 artfynd.xlsx
+++ b/artfynd/A 8803-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381831</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381769</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381770</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381827</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381809</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381963</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,8 +1525,23 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>